--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -12286,12 +12286,12 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -12470,12 +12470,12 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Remove 2 placeholder claim(s); rewrite intro and MCQ angles; review the 2 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
@@ -12746,12 +12746,12 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Remove 2 placeholder claim(s); rewrite intro and MCQ angles; review the 2 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
@@ -12884,12 +12884,12 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Remove 3 placeholder claim(s); rewrite intro and MCQ angles; review the 1 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
@@ -13022,12 +13022,12 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
@@ -13068,12 +13068,12 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>TO DO: replace placeholders</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Remove 1 placeholder claim(s); rewrite intro and MCQ angles; review the 3 remaining claim(s) for accuracy and whether the cited paper supports them; add points if fewer than 4.</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten with high-yield clinical evidence.</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -526,12 +526,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -568,12 +568,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -610,12 +610,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -652,12 +652,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -820,12 +820,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -862,12 +862,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -1576,12 +1576,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -2500,12 +2500,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -2626,12 +2626,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -3172,12 +3172,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -3508,12 +3508,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -3634,12 +3634,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -3676,12 +3676,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -3760,12 +3760,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -4096,12 +4096,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -4558,12 +4558,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -4978,12 +4978,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
@@ -5566,12 +5566,12 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr"/>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -5776,12 +5776,12 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
@@ -5944,12 +5944,12 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
@@ -6028,12 +6028,12 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
@@ -6406,12 +6406,12 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
@@ -6490,12 +6490,12 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -6616,12 +6616,12 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -6826,12 +6826,12 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
@@ -6952,12 +6952,12 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr"/>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
@@ -7246,12 +7246,12 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
@@ -7288,12 +7288,12 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
@@ -7372,12 +7372,12 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
@@ -7498,12 +7498,12 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr"/>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr"/>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr"/>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -7876,12 +7876,12 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
@@ -7918,12 +7918,12 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
@@ -7960,12 +7960,12 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
@@ -8044,12 +8044,12 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr"/>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
@@ -8296,12 +8296,12 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
@@ -8338,12 +8338,12 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
@@ -8548,12 +8548,12 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
@@ -8632,12 +8632,12 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
@@ -8674,12 +8674,12 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
@@ -8716,12 +8716,12 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
@@ -8758,12 +8758,12 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr"/>
@@ -8800,12 +8800,12 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -8926,12 +8926,12 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr"/>
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr"/>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr"/>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr"/>
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
@@ -9304,12 +9304,12 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr"/>
@@ -9430,12 +9430,12 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
@@ -9556,12 +9556,12 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
@@ -9724,12 +9724,12 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr"/>
@@ -9766,12 +9766,12 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
@@ -9808,12 +9808,12 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
@@ -9934,12 +9934,12 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
@@ -10018,12 +10018,12 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
@@ -10102,12 +10102,12 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr"/>
@@ -10144,12 +10144,12 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr"/>
@@ -10228,12 +10228,12 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr"/>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr"/>
@@ -10312,12 +10312,12 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr"/>
@@ -10354,12 +10354,12 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
@@ -10396,12 +10396,12 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
@@ -10480,12 +10480,12 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr"/>
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr"/>
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr"/>
@@ -10606,12 +10606,12 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr"/>
@@ -10648,12 +10648,12 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
@@ -10690,12 +10690,12 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr"/>
@@ -10732,12 +10732,12 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr"/>
@@ -10816,12 +10816,12 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
@@ -10900,12 +10900,12 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
@@ -10942,12 +10942,12 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr"/>

--- a/topic-drafts/topics-373-placeholder-synopses.xlsx
+++ b/topic-drafts/topics-373-placeholder-synopses.xlsx
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
@@ -11068,12 +11068,12 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr"/>
@@ -11110,12 +11110,12 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr"/>
@@ -11152,12 +11152,12 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr"/>
@@ -11194,12 +11194,12 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr"/>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr"/>
@@ -11278,12 +11278,12 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr"/>
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr"/>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
@@ -11488,12 +11488,12 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr"/>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr"/>
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
@@ -11614,12 +11614,12 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
@@ -11698,12 +11698,12 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
@@ -11740,12 +11740,12 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
@@ -11824,12 +11824,12 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
@@ -11908,12 +11908,12 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
@@ -11950,12 +11950,12 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr"/>
@@ -12034,12 +12034,12 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
@@ -12076,12 +12076,12 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
@@ -12118,12 +12118,12 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr"/>
@@ -12244,12 +12244,12 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>TO DO: write from scratch</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>No real content. Remove all placeholder claims; write a new intro, 4 to 5 teaching points, MCQ angles from standard references (or Europe PMC guideline/review/meta-analysis if available).</t>
+          <t>Placeholders removed, intro, teaching points, and MCQ angles rewritten from scratch with clinical evidence.</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr"/>
